--- a/BWI/bestwine_output/bestwine_Belarus.xlsx
+++ b/BWI/bestwine_output/bestwine_Belarus.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA22"/>
+  <dimension ref="A1:AA24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2732,6 +2732,200 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Oao Tabakvintorg</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Oao Tabakvintorg</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>103825</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Belarus</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Homieĺ</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Homieĺskaja voblasć, Homieĺski rajon</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1A Mahilioŭskaja Street</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>246010</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://tabakvintorg.by</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>priemn@tabakvintorg.by</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>+375 232 50-76-43</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>400078357</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>Mozgovoy Vladimir Grigorievich</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Director </t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Oao Tabakvintorg</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Oao Tabakvintorg</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>103825</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Belarus</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Homieĺ</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Homieĺskaja voblasć, Homieĺski rajon</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1A Mahilioŭskaja Street</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>246010</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://tabakvintorg.by</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>priemn@tabakvintorg.by</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>+375 232 50-76-43</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>400078357</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>Koptelova Veronika</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>First Deputy Director</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
